--- a/esyluban/examples/negatives_hard/DataTables/variant_mismatch/t.xlsx
+++ b/esyluban/examples/negatives_hard/DataTables/variant_mismatch/t.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Default" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="En" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,14 +424,14 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="hard.TbVMode" &amp; read_schema_from_file="true"</t>
+          <t>full_name="hard.TbT" &amp; read_schema_from_file="true"</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##</t>
+          <t>##var</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,76 +469,6 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>a</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##export</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>full_name="hard.TbVMode" &amp; read_schema_from_file="true" &amp; variant="en" &amp; mode="list"</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>b</t>
         </is>
       </c>
     </row>
